--- a/data/submission/FILLIT_Warm_Leads.xlsx
+++ b/data/submission/FILLIT_Warm_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warm leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Warm leads'!$A$1:$X$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Warm leads'!$A$1:$W$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X40"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -478,19 +478,18 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -551,65 +550,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Direct no.</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Current supplier</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Current supplier</t>
+          <t>Consumption (as recorded)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Consumption (as recorded)</t>
+          <t>Est. litres / month</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Est. litres / month</t>
+          <t>Fleet / equipment</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Fleet / equipment</t>
+          <t>Pain points</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Pain points</t>
+          <t>Latest comments</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Latest comments</t>
+          <t>First visit</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>First visit</t>
+          <t>Last visit</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Last visit</t>
+          <t>Visits</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Visits</t>
+          <t>Lead source</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Lead source</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Mentions CAFU</t>
         </is>
@@ -618,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BIN YABER DRIVING INSTITUTE</t>
+          <t>Ardh Al Madina Group of Companies</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -639,7 +633,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Dubai (other)</t>
+          <t>Ras Al Khor</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -649,7 +643,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bin Yaber Driving Institute - Head Office, Al Ruwayyah 3, Dubai, UAE</t>
+          <t>Ras Al Khor</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -659,64 +653,72 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Shenaz</t>
+          <t>Anwar Shahzad (Chairman)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>800 293 / +971 4 215 6000</t>
+          <t>556946560 / 563727330</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>508204870</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>info@wahatalmadinatransport@gmail.com</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Musajal Fuel</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>ENOC</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>50-60k L/month</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>55000</v>
+          <t>800 G/day</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>90840</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15+vehicles , 12+ machineries</t>
+        </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>500(mix of petrol &amp;diesel)</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+          <t>Issue with 3rd party quality</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>They have their own tanker to fill their vehicles.
+- Current supplier supplies on credit basis</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="n">
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Emcon Contracting Llc</t>
+          <t>Rhenus Logistics Gulf DWC LLC</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -737,89 +739,83 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Al Quoz</t>
+          <t>Jebel Ali / JAFZA</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Transport, logistics and fleet</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>23rd St - Al Quoz - Al Quoz Industrial Area 3 - Dubai</t>
+          <t>101 Office, Business Park, Building A4 Dubai Logistics City, DWC Jebel Ali Dubai</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Bashir</t>
+          <t>Sasikumar Balaraman (Ocean Freight Manager)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>04 347 3400</t>
+          <t>4 806 1343</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>522434524</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>sasikumar.palaraman@rhenus.com</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Fuel pump (chip)</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Fuel station and 3rd party</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>10000 Gallons / month</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>37850</v>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>40+(12 forklifts, 30+ trucks)</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>70000 L/month</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>70000</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>4 trucks</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Wanted to enquire about price and quotation</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Asked to share more details (price, credits etc. through whatsapp)
--CAFU is not delivering to them</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="n">
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Al Shamsi Boat Factory</t>
+          <t>Emcon Contracting Llc</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -827,97 +823,97 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Ajman Industrial Area</t>
+          <t>Al Quoz</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Marine, boats and shipping</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>P.O. Box 132, Tariq Bin Ziad Street, Mushairef, Ajman, UAE</t>
+          <t>23rd St - Al Quoz - Al Quoz Industrial Area 3 - Dubai</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Abdulsalam Ahamed Falah (Manager)</t>
+          <t>Bashir</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>+971 6-7400330 / +971 6-7400272</t>
+          <t>04 347 3400</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>alshamsi.boat@hotmail.com</t>
+          <t>Fuel station and 3rd party</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Ajwa Diesel Trading</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>7-10k Gallon/month</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>32172</v>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>10 boats currently (depends on manufacturing)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr"/>
+          <t>10000 Gallons / month</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>37850</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>40+(12 forklifts, 30+ trucks)</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Asked to share more details (price, credits etc. through whatsapp)
+-CAFU is not delivering to them</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Consumption depends on delivery country/destination. Looking for credit basis. Asked to mail price quotations.</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>2</v>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Dayal Metal Containers Factory</t>
+          <t>JAIDE Express Freight LLC</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -938,100 +934,79 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ajman Industrial Area</t>
+          <t>Warsan / International City</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Transport, logistics and fleet</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Food &amp; Aerosol Division UAQ, Umm Al Thuoob, Lube Division Ajman Ind. area-1. Paint and Construction Division Ajman New Ind. area-2, UAE</t>
+          <t>France Cluster, R16, Dubai International City, Dubai</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Ajman</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Bilal ( Purchase manager)</t>
-        </is>
-      </c>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>+971 6 7430611</t>
+          <t>+971 4 564 5844</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>552573364</t>
+          <t>info@jadegroup.com</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>aimee.m@dayalmc.com / dheepa@dayalmc.com /sales@dayalmc.com</t>
+          <t>ADNOC (chip)</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (chip)</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>30000L/month+</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>7 forklift, 10 pickups, 1 trailer</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>CAFU is not filling on site</t>
-        </is>
-      </c>
+          <t>150,000 AED/month</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>37500</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>10 trucks</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>CAFU not delivering</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="n">
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Coco Cola Al Ahila Beverage Company</t>
+          <t>Al Shamsi Boat Factory</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1039,89 +1014,96 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Umm Al Quwain</t>
+          <t>Ajman Industrial Area</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>HM5H+WQ5 sales@pacificpaperind.com - UAQ - Sector 5, Emirates industrial Area, Post box 2788 - Umm Al Thuoob - Emirate of Umm Al Quwain</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Umm Al Quwain</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>P.O. Box 132, Tariq Bin Ziad Street, Mushairef, Ajman, UAE</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Abdulsalam Ahamed Falah (Manager)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>+971 6-7400330 / +971 6-7400272</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>alshamsi.boat@hotmail.com</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Ajwa Diesel Trading</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (chip)</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>22,000L/Month</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>22000</v>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>20+ vehicles</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr"/>
+          <t>7-10k Gallon/month</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>32172</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>10 boats currently (depends on manufacturing)</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Consumption depends on delivery country/destination. Looking for credit basis. Asked to mail price quotations.</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Fleet department in DCC. Earlier used 3rd party supplier, shifted to ADNOC (chip) due to war</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Al Jalal Trading Est</t>
+          <t>AFAQ Engineering For Building Contracting lIc</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1142,96 +1124,85 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa, Sharjah</t>
+          <t>Dubai (other)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Office 206, Emirates Industrial City (EIC), Sajaa, Sharjah, UAE</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
+          <t>3, PO BOX No. :83510, Dubai - U.A.E</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>SAYED IRFAN (Pocurement Officer)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>971 6 554 9593</t>
+          <t>52 986 8416 / 48828101</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>561183329</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>Irfan@afaqengineering.com</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>GP Golden</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (prepaid card)</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>20000L/month (both diesel &amp; petrol)</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>12 vehicles</t>
-        </is>
-      </c>
+          <t>8000 Gallons/month+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>30280</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3 trucks and few machinery</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Trust issue with CAFU (took credits)</t>
+          <t>Procuring at 3.4 AED/L(last month) /3.96AED/L(this month)
+- Currently 6 ongoing projects
+- Wants to build long term relationship</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Contract with CAFU in 2025 but they stole their credit</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="n">
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AL BASMA, Detergents &amp; Cleaning Ind LLC</t>
+          <t>Dayal Metal Containers Factory</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1252,84 +1223,95 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Industrial Areas</t>
+          <t>Ajman Industrial Area</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing and factory</t>
+          <t>Metal, steel and aluminium</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Po Box.66454, Sharjah U.A.E</t>
+          <t>Food &amp; Aerosol Division UAQ, Umm Al Thuoob, Lube Division Ajman Ind. area-1. Paint and Construction Division Ajman New Ind. area-2, UAE</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Ismayil</t>
+          <t>Bilal ( Purchase manager)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>06 5351 554 / 55 141 3244 / +971 50 787 5695</t>
+          <t>+971 6 7430611</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>569980488</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>aimee.m@dayalmc.com / dheepa@dayalmc.com /sales@dayalmc.com</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (chip)</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Nearest fuel station</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>18000l/month+</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>18000</v>
+          <t>30000L/month+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7 forklift, 10 pickups, 1 trailer</t>
+        </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2 trucks</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
+          <t>CAFU is not filling on site</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>CAFU not delivering</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>2</v>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Sky Blue Shipping</t>
+          <t>Coco Cola Al Ahila Beverage Company</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1350,80 +1332,75 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Dubai (other)</t>
+          <t>Umm Al Quwain</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Marine, boats and shipping</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>772P+XQF - Kuwait St - Al Raffa - Dubai</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Got business card</t>
-        </is>
-      </c>
+          <t>HM5H+WQ5 sales@pacificpaperind.com - UAQ - Sector 5, Emirates industrial Area, Post box 2788 - Umm Al Thuoob - Emirate of Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (chip)</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Silver home,Jebel Ali port</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>50000AED</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>12500</v>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>3 Trucks</t>
-        </is>
-      </c>
+          <t>22,000L/Month</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>20+ vehicles</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Trucks go to supplier loction to fill</t>
+          <t>Fleet department in DCC. Earlier used 3rd party supplier, shifted to ADNOC (chip) due to war</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Operating Oman to Dubai. Wanted to contact</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n">
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Dar Al Rokham</t>
+          <t>Al Jalal Trading Est</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1444,84 +1421,82 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Jebel Ali / JAFZA</t>
+          <t>Al Sajaa, Sharjah</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Other / unclassified</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Jebel Ali</t>
+          <t>Office 206, Emirates Industrial City (EIC), Sajaa, Sharjah, UAE</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44178642</t>
+          <t>971 6 554 9593</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>mail@dar-al-rokham.com</t>
+          <t>ADNOC (prepaid card)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>ADNOC / ENOC</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>50000 AED+ ( 9000AED+ for forklifts at site, rest for other vehicles)</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>12500</v>
+          <t>20000L/month (both diesel &amp; petrol)</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12 vehicles</t>
+        </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>13+ (3 forklifts, 1 generation, 4 3-ton trucks, 4 6-ton trucks, 1 crane and others)</t>
+          <t>Trust issue with CAFU (took credits)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Diesel quality of 3rd party suppliers is not good
-- CAFU not supplying</t>
+          <t>Contract with CAFU in 2025 but they stole their credit</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Multiple offices</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="n">
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1530,7 +1505,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Al Areen Trading Co LLC</t>
+          <t>AL BASMA, Detergents &amp; Cleaning Ind LLC</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1551,17 +1526,17 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa, Sharjah</t>
+          <t>Sharjah Industrial Areas</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Manufacturing and factory</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Emirates Industrial City, Sajaa, Sharjah (operations also in Deira, Dubai)</t>
+          <t>Po Box.66454, Sharjah U.A.E</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1571,78 +1546,59 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Shafil - Operations
-Shakil - Management</t>
+          <t>Ismayil</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>971 4 221 1782</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Shafil - 0503283454
-Shakil - 0501604847</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>06 5351 554 / 55 141 3244 / +971 50 787 5695</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Nearest fuel station</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (fuel station)</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>10000L/month</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>12 trucks</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>CAFU stopped delivering</t>
-        </is>
-      </c>
+          <t>18000l/month+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2 trucks</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Used to get from CAFU, but CAFU stopped operations</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EcoPack</t>
+          <t>Sky Blue Shipping</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1663,94 +1619,79 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City</t>
+          <t>Dubai (other)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Other / unclassified</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Post Box: 232118 Dubai-U.A.E., Dubai Industrial City</t>
+          <t>772P+XQF - Kuwait St - Al Raffa - Dubai</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Bala Murugan</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>971-4-4326581</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>554997262</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>Got business card</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Silver home,Jebel Ali port</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>ENOC (chip)</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>8500 l/month+ (for months)
-1850 l/month+ (for forklifts)</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>8500</v>
+          <t>50000AED</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>12500</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3 Trucks</t>
+        </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>6 trucks, 3 forklifts</t>
+          <t>Trucks go to supplier loction to fill</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Looking for some USP</t>
+          <t>Operating Oman to Dubai. Wanted to contact</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Operating in multiple countries
-- Currently using go fuel ( CAFU stopped delivering)</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n">
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PROMINENT PRINTING &amp; PUBLISHING CO. L.L.C</t>
+          <t>Dar Al Rokham</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1771,17 +1712,17 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park</t>
+          <t>Jebel Ali / JAFZA</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Plastics and packaging</t>
+          <t>Other / unclassified</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park 1 (DIP-1), Dubai, UAE</t>
+          <t>Jebel Ali</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,70 +1730,74 @@
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Noor</t>
-        </is>
-      </c>
+      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>971 4 880 0804</t>
+          <t>44178642</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>565370279</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>mail@dar-al-rokham.com</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC / ENOC</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>ADNOC(contract), ENOC(fuel pump)</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>8000L per month (all vehicles)</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>8000</v>
+          <t>50000 AED+ ( 9000AED+ for forklifts at site, rest for other vehicles)</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>12500</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>13+ (3 forklifts, 1 generation, 4 3-ton trucks, 4 6-ton trucks, 1 crane and others)</t>
+        </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>8 (1 bus, 7 pickup trucks)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr"/>
+          <t>Diesel quality of 3rd party suppliers is not good
+- CAFU not supplying</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Multiple offices</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>ASked Fillit POC number for scheduling meeting so gave Sarukh sir's number</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n">
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Fast Logistics</t>
+          <t>Al Areen Trading Co LLC</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1873,58 +1818,67 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Warsan / International City</t>
+          <t>Al Sajaa, Sharjah</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Transport, logistics and fleet</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Indigo Optima, 12 International City 1 Street, Dubai</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>Emirates Industrial City, Sajaa, Sharjah (operations also in Deira, Dubai)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Jabir (Operations)</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>544242685</t>
-        </is>
-      </c>
+          <t>Shafil - Operations
+Shakil - Management</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>971 4 221 1782</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>mahendra@fastlogistics.ae</t>
+          <t>ADNOC (fuel station)</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Fuel station</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>5000-8000L/month</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>6500</v>
+          <t>10000L/month</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>12 trucks</t>
+        </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>16 vehicles</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr"/>
+          <t>CAFU stopped delivering</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Used to get from CAFU, but CAFU stopped operations</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Asked us to mail fleet dept. : mahendra@fastlogistics.ae</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1932,25 +1886,24 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="n">
+      <c r="U14" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Ali Rashad Al Shamsi Trd. LCC.</t>
+          <t>EcoPack</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1971,7 +1924,7 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Business Bay / Jumeirah / Barsha</t>
+          <t>Dubai Industrial City</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1981,52 +1934,54 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Deira</t>
+          <t>Post Box: 232118 Dubai-U.A.E., Dubai Industrial City</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Saif</t>
+          <t>Bala Murugan</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>+971 4 229 3282</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>558463530</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>971-4-4326581</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>ENOC (chip)</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (chip)</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>25000 AED/month</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>6250</v>
+          <t>8500 l/month+ (for months)
+1850 l/month+ (for forklifts)</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>6 trucks, 3 forklifts</t>
+        </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>6 trucks, 2 forklifts</t>
+          <t>Looking for some USP</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Bad quality fuel from 3rd party</t>
+          <t>Operating in multiple countries
+- Currently using go fuel ( CAFU stopped delivering)</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>Main office in Deira</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2034,25 +1989,24 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="n">
+      <c r="U15" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FORTIS EASY PANEL FOR PRECAST BUILDING MANUFACTURING CO. L.L.C</t>
+          <t>PROMINENT PRINTING &amp; PUBLISHING CO. L.L.C</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2073,17 +2027,17 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City</t>
+          <t>Dubai Investment Park</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Plastics and packaging</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City, Dubai, UAE</t>
+          <t>Dubai Investment Park 1 (DIP-1), Dubai, UAE</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2093,77 +2047,63 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Umer Farooq (operations head)</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>+971 4 885 6340</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>585585663</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>971 4 880 0804</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC(contract), ENOC(fuel pump)</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Aquiring from FuelBuddy and ADNOC currently. Earlier acquired from CAFU</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4000-5000L/month(boiler) . Unknown for forklifts &amp; trucks</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>12+(7-8 forklifts, 5+trucks)</t>
-        </is>
-      </c>
+          <t>8000L per month (all vehicles)</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8 (1 bus, 7 pickup trucks)</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>CAFU stopped delivering</t>
+          <t>ASked Fillit POC number for scheduling meeting so gave Sarukh sir's number</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Asked for sample and price.
-- They have a transport company as well(space lead transportation)</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="n">
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Burj Al Shaheen Carpentry</t>
+          <t>Fast Logistics</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2171,101 +2111,92 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa, Sharjah</t>
+          <t>Warsan / International City</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Transport, logistics and fleet</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>P.O. Box 43988, Industrial Area, Al Sajja, UAE</t>
+          <t>Indigo Optima, 12 International City 1 Street, Dubai</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Mohd Askam</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>055 3946 340 / 055 1514 910</t>
-        </is>
-      </c>
+          <t>Jabir (Operations)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>553946340</t>
+          <t>mahendra@fastlogistics.ae</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>burjalshaheen4@gmail.com</t>
+          <t>Fuel station</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Nearest fuel station</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>15-20k AED/month</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>4375</v>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>10 trucks</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr"/>
+          <t>5000-8000L/month</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>16 vehicles</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Asked us to mail fleet dept. : mahendra@fastlogistics.ae</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Enquired about fuel quality and price, also credit.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="n">
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Bushehab Launch Factory</t>
+          <t>Ali Rashad Al Shamsi Trd. LCC.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2273,97 +2204,96 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Ajman Industrial Area</t>
+          <t>Business Bay / Jumeirah / Barsha</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Marine, boats and shipping</t>
+          <t>Other / unclassified</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>P.O. Box 2449, Ajman, UAE</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Ajman</t>
-        </is>
-      </c>
+          <t>Deira</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Farag Saad Ismail (Project Manager)</t>
+          <t>Saif</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>+971 544 502 323</t>
+          <t>+971 4 229 3282</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>bushahab14139@gmail.com</t>
+          <t>ADNOC (chip)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Threestar and ADNOC (fuel station)</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Approx. 1,000 Gallon/month (depends on operations/delivery location)</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>3785</v>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
+          <t>25000 AED/month</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>6250</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>6 trucks, 2 forklifts</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Bad quality fuel from 3rd party</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Main office in Deira</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Asked for price and quotation. Enquired about the mobile application and how it works.</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="n">
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Vibe Detergent Trading LLC</t>
+          <t>FORTIS EASY PANEL FOR PRECAST BUILDING MANUFACTURING CO. L.L.C</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2384,84 +2314,92 @@
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Al Jurf, Ajman</t>
+          <t>Dubai Industrial City</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing and factory</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Al Jurf Industrial Area 2, Opposite Al Jurf Mosque, Ajman, United Arab Emirates</t>
+          <t>Dubai Industrial City, Dubai, UAE</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Nishat</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>562910628</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>Umer Farooq (operations head)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 885 6340</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Aquiring from FuelBuddy and ADNOC currently. Earlier acquired from CAFU</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>ENOC, ADNOC (fuel station)</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>15000 AED/month</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>3750</v>
+          <t>4000-5000L/month(boiler) . Unknown for forklifts &amp; trucks</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>12+(7-8 forklifts, 5+trucks)</t>
+        </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>3 pickup, 3 forklifts</t>
+          <t>CAFU stopped delivering</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Need delivery for forklifts</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr"/>
+          <t>Asked for sample and price.
+- They have a transport company as well(space lead transportation)</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="n">
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Daira Carpentry</t>
+          <t>Burj Al Shaheen Carpentry</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2492,56 +2430,52 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Al Sajja Industrial Area, Sharjah, UAE (P.O. Box 71614)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
+          <t>P.O. Box 43988, Industrial Area, Al Sajja, UAE</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Masood Ahmed (Manager) / Naimat Ullah (CEO)</t>
+          <t>Mohd Askam</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>+971 54 7027 226 / +971 52 7124 660</t>
+          <t>055 3946 340 / 055 1514 910</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>+971 54 7027 226 / +971 52 7124 660</t>
+          <t>burjalshaheen4@gmail.com</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>manager@dairacarpentry.com / dairacarpentry1@gmail.com</t>
+          <t>Nearest fuel station</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (fuel station)</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>12-15k AED/month</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>3375</v>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>19 trucks</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr"/>
+          <t>15-20k AED/month</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>4375</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>10 trucks</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Enquired about fuel quality and price, also credit.</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Facing problems with ADNOC chip, need to topup. Consumption approx. 3,500 AED/day (~1,05,000 AED/month).</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2549,25 +2483,20 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Bu Humaid Contracting</t>
+          <t>Point Pinnacle Building Contracting LLC</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2575,20 +2504,20 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Ajman Industrial Area</t>
+          <t>Business Bay / Jumeirah / Barsha</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2598,83 +2527,73 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Ajman Boulevard - Al Jerf 2 - Ajman</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Ajman</t>
-        </is>
-      </c>
+          <t>Unit No. 201 &amp; 202, 2nd Floor Saeed Harbe Building 10th A Street, Port Saeed Deira, Dubai. UAE</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Ameen Elian</t>
+          <t>Mr. Hakeem</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>06 746 8222</t>
+          <t>50 132 9600 / 4232 4117</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>501966376</t>
+          <t>hr@ppbcontracting.com</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>info@buhumaidco.com / ameen.elian@buhumaidco.com</t>
+          <t>Al Quoz Diesel</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3rd party</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100-300 G/week</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>3278</v>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Multiple machinery and generators</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
+          <t>15000-20000 AED/month</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>4375</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2 generators and multiple rental vehicles</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Currently having a 2 year project (Villa DAMAS)</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>They have their own tanker ( they fill their vehicle via their own tanker).
-- Asked to share via email</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="n">
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Gutmann</t>
+          <t>Bushehab Launch Factory</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2682,97 +2601,96 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park</t>
+          <t>Ajman Industrial Area</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing and factory</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park 2, Dubai, UAE</t>
+          <t>P.O. Box 2449, Ajman, UAE</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Mohamed Farag Saad Ismail (Project Manager)</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>971 4 808 0500</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>+971 544 502 323</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>bushahab14139@gmail.com</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>info@gutmannme.com</t>
+          <t>Threestar and ADNOC (fuel station)</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Unknown ( from Al Quoz)</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>10000AED (not sure about quantity, only aware about price)</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>15 (10 vehicles , 5 forklifts)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr"/>
+          <t>Approx. 1,000 Gallon/month (depends on operations/delivery location)</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>3785</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Asked for price and quotation. Enquired about the mobile application and how it works.</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Asked to write mailto : info@gutmannme.com for all the information</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="n">
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>OP3 Design</t>
+          <t>Vibe Detergent Trading LLC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2793,88 +2711,79 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Dubai Industrial City</t>
+          <t>Al Jurf, Ajman</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Other / unclassified</t>
+          <t>Manufacturing and factory</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Saih Shuaib 4,Roundabout 6, Dubai Industrial City, Dubai, United Arab Emirates</t>
+          <t>Al Jurf Industrial Area 2, Opposite Al Jurf Mosque, Ajman, United Arab Emirates</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Amaan Khan (Purchase manager)</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>509816520</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>509816520</t>
-        </is>
-      </c>
+          <t>Nishat</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>amaan@op3global.com</t>
+          <t>ENOC, ADNOC (fuel station)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Fuel station</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>10000 AED/month+</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>2500</v>
+          <t>15000 AED/month</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>3750</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>3 pickup, 3 forklifts</t>
+        </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Need delivery for forklifts</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="n">
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ascend Metal Industries</t>
+          <t>Daira Carpentry</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2882,97 +2791,100 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Jebel Ali / JAFZA</t>
+          <t>Al Sajaa, Sharjah</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Jebel Ali Industrial Area - 3, Dubai</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Al Sajja Industrial Area, Sharjah, UAE (P.O. Box 71614)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Kaid Rampurwala (purchase department)</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>Masood Ahmed (Manager) / Naimat Ullah (CEO)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>+971 54 7027 226 / +971 52 7124 660</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>581032667</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>manager@dairacarpentry.com / dairacarpentry1@gmail.com</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (fuel station)</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Third party (bedford fuel trading)</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>2000L/month</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1 bus, 2 forklifts</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr"/>
+          <t>12-15k AED/month</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>3375</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>19 trucks</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Facing problems with ADNOC chip, need to topup. Consumption approx. 3,500 AED/day (~1,05,000 AED/month).</t>
+        </is>
+      </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Tried CAFU for petrol</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="n">
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Muhammad Abbas Metal Scrap Tr. LLC</t>
+          <t>Bu Humaid Contracting</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2993,88 +2905,88 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa, Sharjah</t>
+          <t>Ajman Industrial Area</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Sajja Industrial Area, Sharjah, UAE</t>
+          <t>Ajman Boulevard - Al Jerf 2 - Ajman</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Mehran Hameed (Managing Director)</t>
+          <t>Ameen Elian</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>+971 55 538 1786</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>06 746 8222</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>info@buhumaidco.com / ameen.elian@buhumaidco.com</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>redlinedevoted@gmail.com / master.1624@yahoo.com</t>
+          <t>3rd party</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Closest fuel station</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>7-8k AED/month</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>1875</v>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>4 trucks, 4 forklifts</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr"/>
+          <t>100-300 G/week</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>3278</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Multiple machinery and generators</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>They have their own tanker ( they fill their vehicle via their own tanker).
+- Asked to share via email</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Forklift gets fuel by tanks. Asked about price, delivery charges, quality of fuel, and time to reach site.</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="n">
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Main Crete Building Contracting</t>
+          <t>Gutmann</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3095,17 +3007,17 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Al Quoz</t>
+          <t>Dubai Investment Park</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Manufacturing and factory</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Al QuozAl - Al Khail Rd - Al Quoz - Al Quoz Industrial Area 2 - Dubai</t>
+          <t>Dubai Investment Park 2, Dubai, UAE</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3116,67 +3028,62 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>04 513 9794</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>971 4 808 0500</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>info@gutmannme.com</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>vs@maincrete.com</t>
+          <t>Unknown ( from Al Quoz)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>ADNOC, ENOC</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>400l/week</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>1732</v>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3 generators, 1car, 1 bus</t>
-        </is>
-      </c>
+          <t>10000AED (not sure about quantity, only aware about price)</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>15 (10 vehicles , 5 forklifts)</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>No trust on door step delivery</t>
+          <t>Asked to write mailto : info@gutmannme.com for all the information</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Diesel filled at site for machinery and on fuel pump for vehichels</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="n">
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Windsor Foodstuff Factory Llc</t>
+          <t>OP3 Design</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3197,88 +3104,83 @@
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Industrial Areas</t>
+          <t>Dubai Industrial City</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Other / unclassified</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>P. O. Box No. 65821, Sharjah, United Arab Emirates</t>
+          <t>Saih Shuaib 4,Roundabout 6, Dubai Industrial City, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Shailesh Kumar</t>
+          <t>Amaan Khan (Purchase manager)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>+971 6 5434808</t>
+          <t>509816520</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65434808</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>amaan@op3global.com</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Fuel station</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3rd party from Ajman</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>200-600 gallons/month based on season</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>1514</v>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1 boiler</t>
-        </is>
-      </c>
+          <t>10000 AED/month+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Price sensitive</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Maqad Building Cintracting</t>
+          <t>Ascend Metal Industries</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3299,88 +3201,79 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Dubai Silicon Oasis</t>
+          <t>Jebel Ali / JAFZA</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Metal, steel and aluminium</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Silicon Oasis</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
+          <t>Jebel Ali Industrial Area - 3, Dubai</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Nikhil</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>42842055</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>42842055</t>
-        </is>
-      </c>
+          <t>Kaid Rampurwala (purchase department)</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>accounts@maqad.co</t>
+          <t>Third party (bedford fuel trading)</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>ENOC</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>5000 AED/month</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>6 vehicles+, 3 generators</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
+          <t>2000L/month</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1 bus, 2 forklifts</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Tried CAFU for petrol</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="n">
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Rukun Al Emdad spare parts</t>
+          <t>Muhammad Abbas Metal Scrap Tr. LLC</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3388,30 +3281,30 @@
           <t>Warm</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Sharjah Industrial Areas</t>
+          <t>Al Sajaa, Sharjah</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Auto workshop and equipment</t>
+          <t>Metal, steel and aluminium</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>238 First Industrial Street, Sharjah, Ash Shāriqah</t>
+          <t>Sajja Industrial Area, Sharjah, UAE</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3421,72 +3314,67 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Inayat</t>
+          <t>Mehran Hameed (Managing Director)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>557622755</t>
+          <t>+971 55 538 1786</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>557622755</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>redlinedevoted@gmail.com / master.1624@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Closest fuel station</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>CAFU</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>5000 AED/month+</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>1250</v>
+          <t>7-8k AED/month</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>1875</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>4 trucks, 4 forklifts</t>
+        </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Delivery fee</t>
+          <t>Forklift gets fuel by tanks. Asked about price, delivery charges, quality of fuel, and time to reach site.</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Getting from CAFU with extra delivery fee</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="n">
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Self-generated</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>North Africa Shipping</t>
+          <t>Main Crete Building Contracting</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3507,17 +3395,17 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Nadd Al Hamar</t>
+          <t>Al Quoz</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Marine, boats and shipping</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Plot 59MJ+PM7, Nadd Al Hamar</t>
+          <t>Al QuozAl - Al Khail Rd - Al Quoz - Al Quoz Industrial Area 2 - Dubai</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3525,74 +3413,69 @@
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Hamoud</t>
-        </is>
-      </c>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>506581241</t>
+          <t>04 513 9794</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>506581241</t>
+          <t>vs@maincrete.com</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>aboumouad4@hotmail.com</t>
+          <t>ADNOC, ENOC</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Trident diesel</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>2500 AED+ (based on requirement)</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>625</v>
+          <t>400l/week</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>1732</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>3 generators, 1car, 1 bus</t>
+        </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>14 (12 trucks, 2 forklifts)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr"/>
+          <t>No trust on door step delivery</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Diesel filled at site for machinery and on fuel pump for vehichels</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>They speak in arabic</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="n">
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Stone craft marbles &amp; granites</t>
+          <t>Windsor Foodstuff Factory Llc</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3618,12 +3501,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Plot 32, 12th Street, Industrial Area 17</t>
+          <t>P. O. Box No. 65821, Sharjah, United Arab Emirates</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3633,72 +3516,63 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Zakir</t>
+          <t>Shailesh Kumar</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>504955895</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>504955895</t>
-        </is>
-      </c>
+          <t>+971 6 5434808</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>stonecraftmarbles@gmail.com</t>
+          <t>3rd party from Ajman</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Fuel pump</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>300 L/month +</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1 forklift</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr"/>
+          <t>200-600 gallons/month based on season</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>1514</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1 boiler</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Price sensitive</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Using diesel ( based on requirement)</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LSC Freights and Logistics</t>
+          <t>Bildco Aerated Concrete Products LLC</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3719,74 +3593,87 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Business Bay / Jumeirah / Barsha</t>
+          <t>Dubai Industrial City</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Transport, logistics and fleet</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Karama, Near GPO</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>Dubai - Saih Shuaib 4 - Dubai Industrial City - Dubai</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Mr Nicolas</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 427 0335</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>majed@bildco.ae</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Welcome Diesel</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Multiple vedors(cafu, enoc)</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>50+ Vechiles</t>
-        </is>
-      </c>
+          <t>1500 litres/month (For 8 forklifts), 4000 litres/month (For 1 truck)</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1 truck, 8 forklifts</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Don't trust vendors because of price.</t>
+          <t>He will convert if we provide lower than market price</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>No monthly contracts due to price fluctuation. Got business card(Rahul) - very knowledgeble. Knows diesel quality and test it. Pain point - Don't trust vendors because of price. Very intrested in companies who provide credit.</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="n">
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Melcome Luxury Transport</t>
+          <t>Maqad Building Cintracting</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3807,70 +3694,83 @@
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Business Bay / Jumeirah / Barsha</t>
+          <t>Dubai Silicon Oasis</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Marine, boats and shipping</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Office Land Building - 46B St - Al Karama - Dubai</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Silicon Oasis</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Got business card</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>Nikhil</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>42842055</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>accounts@maqad.co</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>ENOC</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>ENOC</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="n"/>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>40(mix of petrol &amp; diesel)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Go to fuel Station</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr"/>
+          <t>5000 AED/month</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>6 vehicles+, 3 generators</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AL SAHEB BLDG MAT TR L.L.C.</t>
+          <t>Rukun Al Emdad spare parts</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3891,17 +3791,17 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa, Sharjah</t>
+          <t>Sharjah Industrial Areas</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Other / unclassified</t>
+          <t>Auto workshop and equipment</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Al Sajaa Industrial Area, Sharjah</t>
+          <t>238 First Industrial Street, Sharjah, Ash Shāriqah</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -3911,62 +3811,58 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Mohd. Shoaib</t>
+          <t>Inayat</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>971 6 533 8751</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>544591752</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>557622755</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>CAFU</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Emarat (pump)</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="n"/>
+          <t>5000 AED/month+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>3 trailers(10t, 4t, 3t), 4 forklifts(10t, 5t, 4t, 3t)
- t = Tons</t>
+          <t>Delivery fee</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>CAFU not filling forklifts</t>
+          <t>Getting from CAFU with extra delivery fee</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Asked for diesel sample for quality check</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="n">
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3975,7 +3871,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ECOCOAST CONTRACTING L.L.C</t>
+          <t>North Africa Shipping</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3996,17 +3892,17 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park</t>
+          <t>Nadd Al Hamar</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Building and civil contracting</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park 2, Dubai, UAE</t>
+          <t>Plot 59MJ+PM7, Nadd Al Hamar</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4014,70 +3910,69 @@
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Hamoud</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>+971 4 885 1996</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>506581241</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>aboumouad4@hotmail.com</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Trident diesel</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Fuel pumps</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Less consumption in dubai(1 truck).
-- Unknown consumption in UAQ</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1 in Dubai.
-- Unknown inUAQ</t>
-        </is>
-      </c>
+          <t>2500 AED+ (based on requirement)</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>14 (12 trucks, 2 forklifts)</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Earlier used to procure from CAFU. Stopped due to bad service</t>
+          <t>They speak in arabic</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Also operating in Um Al Quwain</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="n">
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Gulf Duct Industries LLC</t>
+          <t>Stone craft marbles &amp; granites</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -4098,82 +3993,87 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park</t>
+          <t>Sharjah Industrial Areas</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing and factory</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park 2 (DIP 2), Dubai, UAE</t>
+          <t>Plot 32, 12th Street, Industrial Area 17</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Javed Patwe (Purchase dept.)</t>
+          <t>Zakir</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>971 4 887 7269</t>
+          <t>504955895</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>557579597</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>stonecraftmarbles@gmail.com</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Fuel pump</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>8(6 trucks, 1 bus, 1 forklift)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr"/>
+          <t>300 L/month +</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1 forklift</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Using diesel ( based on requirement)</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>They get delivery onsite. Unable to meet correct POC but got business card</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="n">
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HARVEY AND BROCKLESS FOODSTUFF TRADING LLC</t>
+          <t>LSC Freights and Logistics</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -4194,91 +4094,73 @@
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Dubai Investment Park</t>
+          <t>Business Bay / Jumeirah / Barsha</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Transport, logistics and fleet</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7th Central Logistic Hub, Block A, Dubai Investment Park 1, Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Purchase manager</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>971 503916734</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>503916734</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>ADNOC and 3rd third parties</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="n"/>
+          <t>Karama, Near GPO</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Multiple vedors(cafu, enoc)</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>50+ Vechiles</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>15 trucks</t>
+          <t>Don't trust vendors because of price.</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>All good</t>
+          <t>No monthly contracts due to price fluctuation. Got business card(Rahul) - very knowledgeble. Knows diesel quality and test it. Pain point - Don't trust vendors because of price. Very intrested in companies who provide credit.</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Already aware about Fillit.
-- Purchase manager was absent so talked to him over call</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="n">
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Ideal Steel Construction Contractin</t>
+          <t>Melcome Luxury Transport</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -4299,83 +4181,69 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Al Quoz</t>
+          <t>Business Bay / Jumeirah / Barsha</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Metal, steel and aluminium</t>
+          <t>Marine, boats and shipping</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24 6A Street - Al Quoz - Al Quoz Industrial Area 3 - Dubai</t>
+          <t>Office Land Building - 46B St - Al Karama - Dubai</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Shankar</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>04 330 0071</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>565332951</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+          <t>Got business card</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>ENOC</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>40(mix of petrol &amp; diesel)</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>13 vehicles (3+buses, 4+pickups, 1 tipper, 2 forklifts)</t>
+          <t>Go to fuel Station</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Fuel required at sites
-- Tried CAFU earlier</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="n">
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Sidco Foods</t>
+          <t>AL SAHEB BLDG MAT TR L.L.C.</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4396,90 +4264,86 @@
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Dubai (other)</t>
+          <t>Al Sajaa, Sharjah</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Other / unclassified</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Umm Ramool, Dubai, UAE</t>
+          <t>Al Sajaa Industrial Area, Sharjah</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Aquib</t>
+          <t>Mohd. Shoaib</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>971 4 264 2247</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>585997143</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>ENOC &amp; EPPCO</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>Based on requirement (every night)</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n"/>
+          <t>971 6 533 8751</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Emarat (pump)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>3 trailers(10t, 4t, 3t), 4 forklifts(10t, 5t, 4t, 3t)
+ t = Tons</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>25(22-23 trucks, 1 bus, 1 long container)</t>
+          <t>CAFU not filling forklifts</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>No pain points</t>
+          <t>Asked for diesel sample for quality check</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Unable to meet higher management because of monday morning meetings.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="n">
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Sun Bright Plastic Factory Llc</t>
+          <t>ECOCOAST CONTRACTING L.L.C</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -4500,76 +4364,662 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Al Jurf, Ajman</t>
+          <t>Dubai Investment Park</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Plastics and packaging</t>
+          <t>Building and civil contracting</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Jurf Industrial Area, P. O. Box No. 4877, Ajman, United Arab Emirates</t>
+          <t>Dubai Investment Park 2, Dubai, UAE</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>+971 6 7487466</t>
+          <t>+971 4 885 1996</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
+          <t>Fuel pumps</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Less consumption in dubai(1 truck).
+- Unknown consumption in UAQ</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>1 in Dubai.
+- Unknown inUAQ</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Earlier used to procure from CAFU. Stopped due to bad service</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Also operating in Um Al Quwain</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Gulf Duct Industries LLC</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Dubai Investment Park</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing and factory</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Dubai Investment Park 2 (DIP 2), Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Javed Patwe (Purchase dept.)</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>971 4 887 7269</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>8(6 trucks, 1 bus, 1 forklift)</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>They get delivery onsite. Unable to meet correct POC but got business card</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HARVEY AND BROCKLESS FOODSTUFF TRADING LLC</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Dubai Investment Park</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Food and beverage</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>7th Central Logistic Hub, Block A, Dubai Investment Park 1, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Purchase manager</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>971 503916734</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC and 3rd third parties</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>15 trucks</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>All good</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Already aware about Fillit.
+- Purchase manager was absent so talked to him over call</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Ideal Steel Construction Contractin</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Al Quoz</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Metal, steel and aluminium</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>24 6A Street - Al Quoz - Al Quoz Industrial Area 3 - Dubai</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Shankar</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>04 330 0071</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>ENOC</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>13 vehicles (3+buses, 4+pickups, 1 tipper, 2 forklifts)</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Fuel required at sites
+- Tried CAFU earlier</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Sidco Foods</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Dubai (other)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Food and beverage</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Umm Ramool, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Aquib</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>971 4 264 2247</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>ENOC &amp; EPPCO</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Based on requirement (every night)</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>25(22-23 trucks, 1 bus, 1 long container)</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>No pain points</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Unable to meet higher management because of monday morning meetings.</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Sun Bright Plastic Factory Llc</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Al Jurf, Ajman</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Plastics and packaging</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Jurf Industrial Area, P. O. Box No. 4877, Ajman, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>+971 6 7487466</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
           <t>info@brightplasticuae.com</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>ADNOC fuel station</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>1 forklift, 2 3-ton trucks</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>Changed the name to Bright Plastic</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr">
+      <c r="T45" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="V40" s="2" t="n">
+      <c r="U45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Planned list</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TTS International Heavy Lift Solution Services LLC</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Dubai (other)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Other / unclassified</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>PO Box : 416929, Dubai</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Rishidas C</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>507539705</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>rishidas@ttsinternational.ae</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Nearest Fuel Station</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Based on supplier</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>6 diesel vehicles</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Delivery charges by 3rd party</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Site in DIC.
+- Enquired about price and delivery charges</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X40"/>
+  <autoFilter ref="A1:W46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>